--- a/results/Q1/result1.xlsx
+++ b/results/Q1/result1.xlsx
@@ -1919,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col width="11.6328125" customWidth="1" style="4" min="1" max="3"/>
@@ -1959,13 +1959,18 @@
           <t>0:00-4:00</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>4499.999999999999</v>
+      </c>
       <c r="C2" t="n">
-        <v>4499.999999999999</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -1975,13 +1980,18 @@
           <t>4:00-8:00</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>833.3333333333333</v>
+      </c>
       <c r="C3" t="n">
-        <v>833.3333333333333</v>
-      </c>
-      <c r="D3" s="6" t="n">
         <v>6365.8412</v>
       </c>
-      <c r="F3" t="n">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -1991,10 +2001,10 @@
           <t>8:00-12:00</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>4787.964288065848</v>
+      </c>
       <c r="C4" t="n">
-        <v>4787.964288065848</v>
-      </c>
-      <c r="D4" t="n">
         <v>1702.996983333333</v>
       </c>
     </row>
@@ -2004,10 +2014,10 @@
           <t>12:00-16:00</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>5286.035176954731</v>
+      </c>
       <c r="C5" t="n">
-        <v>5286.035176954731</v>
-      </c>
-      <c r="D5" t="n">
         <v>91.1013833333335</v>
       </c>
     </row>
@@ -2017,10 +2027,10 @@
           <t>16:00-20:00</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
         <v>5780.131883333333</v>
       </c>
     </row>
@@ -2030,10 +2040,10 @@
           <t>20:00-24:00</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>5333.333333333332</v>
+      </c>
       <c r="C7" t="n">
-        <v>5333.333333333332</v>
-      </c>
-      <c r="D7" t="n">
         <v>2859.868116666667</v>
       </c>
     </row>
